--- a/src/prommis/solvent_extraction/SX_optimization_results.xlsx
+++ b/src/prommis/solvent_extraction/SX_optimization_results.xlsx
@@ -8,20 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ad00105\Desktop\Model_software\prommis\src\prommis\solvent_extraction\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9FF7045-3DF5-481F-A6EF-70BB5CB0A946}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B74C2C2F-F158-4BB1-B7EB-4BD1C413464F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-25320" yWindow="1785" windowWidth="25440" windowHeight="15270" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0" iterate="1" iterateCount="10000"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="18">
   <si>
     <t>lb</t>
   </si>
@@ -81,7 +82,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -114,8 +115,14 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -146,8 +153,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF81"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -185,11 +198,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -224,6 +252,19 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -232,7 +273,7 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
-      <color rgb="FFF8F9CB"/>
+      <color rgb="FFFFFF81"/>
     </mruColors>
   </colors>
   <extLst>
@@ -1108,7 +1149,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.140625" style="8"/>
+    <col min="2" max="2" width="9.140625" style="8" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -1616,4 +1657,595 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:N14"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="32.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" style="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B1" s="18">
+        <v>1</v>
+      </c>
+      <c r="C1" s="16">
+        <v>2</v>
+      </c>
+      <c r="D1" s="16">
+        <v>3</v>
+      </c>
+      <c r="E1" s="16">
+        <v>4</v>
+      </c>
+      <c r="F1" s="16">
+        <v>5</v>
+      </c>
+      <c r="G1" s="16">
+        <v>6</v>
+      </c>
+      <c r="H1" s="16">
+        <v>7</v>
+      </c>
+      <c r="I1" s="16">
+        <v>8</v>
+      </c>
+      <c r="J1" s="16">
+        <v>9</v>
+      </c>
+      <c r="K1" s="16">
+        <v>10</v>
+      </c>
+      <c r="L1" s="16">
+        <v>11</v>
+      </c>
+      <c r="M1" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="16" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A2" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="8">
+        <v>1.3</v>
+      </c>
+      <c r="C2">
+        <v>1.3</v>
+      </c>
+      <c r="D2">
+        <v>1.3</v>
+      </c>
+      <c r="E2">
+        <v>1.3</v>
+      </c>
+      <c r="F2">
+        <v>1.3</v>
+      </c>
+      <c r="G2">
+        <v>1.3</v>
+      </c>
+      <c r="H2">
+        <v>1.3</v>
+      </c>
+      <c r="I2">
+        <v>1.3</v>
+      </c>
+      <c r="J2">
+        <v>1.3</v>
+      </c>
+      <c r="K2">
+        <v>1.3</v>
+      </c>
+      <c r="L2">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A3" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="8">
+        <v>16</v>
+      </c>
+      <c r="C3">
+        <v>16</v>
+      </c>
+      <c r="D3">
+        <v>16</v>
+      </c>
+      <c r="E3">
+        <v>16</v>
+      </c>
+      <c r="F3">
+        <v>16</v>
+      </c>
+      <c r="G3">
+        <v>16</v>
+      </c>
+      <c r="H3">
+        <v>16</v>
+      </c>
+      <c r="I3">
+        <v>16</v>
+      </c>
+      <c r="J3">
+        <v>16</v>
+      </c>
+      <c r="K3">
+        <v>16</v>
+      </c>
+      <c r="L3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A4" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="8">
+        <v>0.1</v>
+      </c>
+      <c r="C4">
+        <v>0.1</v>
+      </c>
+      <c r="D4">
+        <v>0.1</v>
+      </c>
+      <c r="E4">
+        <v>0.1</v>
+      </c>
+      <c r="F4">
+        <v>0.1</v>
+      </c>
+      <c r="G4">
+        <v>0.1</v>
+      </c>
+      <c r="H4">
+        <v>0.1</v>
+      </c>
+      <c r="I4">
+        <v>0.1</v>
+      </c>
+      <c r="J4">
+        <v>0.1</v>
+      </c>
+      <c r="K4">
+        <v>0.1</v>
+      </c>
+      <c r="L4">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A5" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="8">
+        <v>6</v>
+      </c>
+      <c r="C5">
+        <v>6</v>
+      </c>
+      <c r="D5">
+        <v>6</v>
+      </c>
+      <c r="E5">
+        <v>6</v>
+      </c>
+      <c r="F5">
+        <v>6</v>
+      </c>
+      <c r="G5">
+        <v>6</v>
+      </c>
+      <c r="H5">
+        <v>6</v>
+      </c>
+      <c r="I5">
+        <v>6</v>
+      </c>
+      <c r="J5">
+        <v>6</v>
+      </c>
+      <c r="K5">
+        <v>6</v>
+      </c>
+      <c r="L5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="8">
+        <v>31.585999999999999</v>
+      </c>
+      <c r="C6" s="5">
+        <v>31.489000000000001</v>
+      </c>
+      <c r="D6" s="5">
+        <v>31.343</v>
+      </c>
+      <c r="E6" s="5">
+        <v>31.14</v>
+      </c>
+      <c r="F6" s="5">
+        <v>30.827000000000002</v>
+      </c>
+      <c r="G6" s="5">
+        <v>30.209</v>
+      </c>
+      <c r="H6" s="5">
+        <v>29.48</v>
+      </c>
+      <c r="I6" s="5">
+        <v>28.632000000000001</v>
+      </c>
+      <c r="J6" s="5">
+        <v>27.324999999999999</v>
+      </c>
+      <c r="K6" s="5">
+        <v>26.201000000000001</v>
+      </c>
+      <c r="L6" s="5">
+        <v>24.972999999999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="8">
+        <v>5.8999999999999997E-2</v>
+      </c>
+      <c r="C7" s="5">
+        <v>0.05</v>
+      </c>
+      <c r="D7" s="5">
+        <v>0.04</v>
+      </c>
+      <c r="E7" s="5">
+        <v>0.03</v>
+      </c>
+      <c r="F7" s="5">
+        <v>0.02</v>
+      </c>
+      <c r="G7" s="5">
+        <v>0.01</v>
+      </c>
+      <c r="H7" s="5">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="I7" s="5">
+        <v>2E-3</v>
+      </c>
+      <c r="J7" s="5">
+        <v>1E-3</v>
+      </c>
+      <c r="K7" s="5">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="L7" s="5">
+        <v>2.5000000000000001E-4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" s="20" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="8">
+        <v>4999.1229999999996</v>
+      </c>
+      <c r="C8" s="20">
+        <v>5000</v>
+      </c>
+      <c r="D8" s="20">
+        <v>5000</v>
+      </c>
+      <c r="E8" s="20">
+        <v>5000</v>
+      </c>
+      <c r="F8" s="20">
+        <v>5000</v>
+      </c>
+      <c r="G8" s="20">
+        <v>5000</v>
+      </c>
+      <c r="H8" s="20">
+        <v>5000</v>
+      </c>
+      <c r="I8" s="20">
+        <v>5000</v>
+      </c>
+      <c r="J8" s="20">
+        <v>5000</v>
+      </c>
+      <c r="K8" s="20">
+        <v>5000</v>
+      </c>
+      <c r="L8" s="20">
+        <v>4999.9930000000004</v>
+      </c>
+      <c r="M8" s="20">
+        <v>1200</v>
+      </c>
+      <c r="N8" s="20">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" s="20" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="8">
+        <v>0.56300000000000006</v>
+      </c>
+      <c r="C9" s="20">
+        <v>0.56100000000000005</v>
+      </c>
+      <c r="D9" s="20">
+        <v>0.55800000000000005</v>
+      </c>
+      <c r="E9" s="20">
+        <v>0.55400000000000005</v>
+      </c>
+      <c r="F9" s="20">
+        <v>0.54800000000000004</v>
+      </c>
+      <c r="G9" s="20">
+        <v>0.53500000000000003</v>
+      </c>
+      <c r="H9" s="20">
+        <v>0.52100000000000002</v>
+      </c>
+      <c r="I9" s="20">
+        <v>0.504</v>
+      </c>
+      <c r="J9" s="20">
+        <v>0.47599999999999998</v>
+      </c>
+      <c r="K9" s="20">
+        <v>0.45200000000000001</v>
+      </c>
+      <c r="L9" s="20">
+        <v>0.42399999999999999</v>
+      </c>
+      <c r="M9" s="20">
+        <v>0.1</v>
+      </c>
+      <c r="N9" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" s="20" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="8">
+        <v>20.010000000000002</v>
+      </c>
+      <c r="C10" s="20">
+        <v>20.010000000000002</v>
+      </c>
+      <c r="D10" s="20">
+        <v>20.010000000000002</v>
+      </c>
+      <c r="E10" s="20">
+        <v>20.010000000000002</v>
+      </c>
+      <c r="F10" s="20">
+        <v>20.010000000000002</v>
+      </c>
+      <c r="G10" s="20">
+        <v>20.010000000000002</v>
+      </c>
+      <c r="H10" s="20">
+        <v>20.010000000000002</v>
+      </c>
+      <c r="I10" s="20">
+        <v>20.010000000000002</v>
+      </c>
+      <c r="J10" s="20">
+        <v>20.010000000000002</v>
+      </c>
+      <c r="K10" s="20">
+        <v>20.010000000000002</v>
+      </c>
+      <c r="L10" s="20">
+        <v>20.010000000000002</v>
+      </c>
+      <c r="M10" s="20">
+        <v>20.010000000000002</v>
+      </c>
+      <c r="N10" s="20">
+        <v>80.010000000000005</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" s="20" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="8">
+        <v>79.92</v>
+      </c>
+      <c r="C11" s="20">
+        <v>80.009</v>
+      </c>
+      <c r="D11" s="20">
+        <v>80.009</v>
+      </c>
+      <c r="E11" s="20">
+        <v>80.009</v>
+      </c>
+      <c r="F11" s="20">
+        <v>80.009</v>
+      </c>
+      <c r="G11" s="20">
+        <v>80.009</v>
+      </c>
+      <c r="H11" s="20">
+        <v>80.009</v>
+      </c>
+      <c r="I11" s="20">
+        <v>80.009</v>
+      </c>
+      <c r="J11" s="20">
+        <v>80.010000000000005</v>
+      </c>
+      <c r="K11" s="20">
+        <v>80.010000000000005</v>
+      </c>
+      <c r="L11" s="20">
+        <v>80.001999999999995</v>
+      </c>
+      <c r="M11" s="20">
+        <v>20.010000000000002</v>
+      </c>
+      <c r="N11" s="20">
+        <v>80.010000000000005</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" s="20" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" s="8">
+        <v>3</v>
+      </c>
+      <c r="C12" s="20">
+        <v>3</v>
+      </c>
+      <c r="D12" s="20">
+        <v>3</v>
+      </c>
+      <c r="E12" s="20">
+        <v>3</v>
+      </c>
+      <c r="F12" s="20">
+        <v>3</v>
+      </c>
+      <c r="G12" s="20">
+        <v>3</v>
+      </c>
+      <c r="H12" s="20">
+        <v>3</v>
+      </c>
+      <c r="I12" s="20">
+        <v>3</v>
+      </c>
+      <c r="J12" s="20">
+        <v>3</v>
+      </c>
+      <c r="K12" s="20">
+        <v>3</v>
+      </c>
+      <c r="L12" s="20">
+        <v>2.9990000000000001</v>
+      </c>
+      <c r="M12" s="20">
+        <v>0.1</v>
+      </c>
+      <c r="N12" s="20">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" s="20" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="8">
+        <v>3</v>
+      </c>
+      <c r="C13" s="20">
+        <v>3</v>
+      </c>
+      <c r="D13" s="20">
+        <v>3</v>
+      </c>
+      <c r="E13" s="20">
+        <v>3</v>
+      </c>
+      <c r="F13" s="20">
+        <v>3</v>
+      </c>
+      <c r="G13" s="20">
+        <v>3</v>
+      </c>
+      <c r="H13" s="20">
+        <v>3</v>
+      </c>
+      <c r="I13" s="20">
+        <v>3</v>
+      </c>
+      <c r="J13" s="20">
+        <v>3</v>
+      </c>
+      <c r="K13" s="20">
+        <v>3</v>
+      </c>
+      <c r="L13" s="20">
+        <v>2.9990000000000001</v>
+      </c>
+      <c r="M13" s="20">
+        <v>0.1</v>
+      </c>
+      <c r="N13" s="20">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" s="20" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" s="8">
+        <v>2.827</v>
+      </c>
+      <c r="C14" s="20">
+        <v>2.9990000000000001</v>
+      </c>
+      <c r="D14" s="20">
+        <v>2.9990000000000001</v>
+      </c>
+      <c r="E14" s="20">
+        <v>2.9990000000000001</v>
+      </c>
+      <c r="F14" s="20">
+        <v>2.9990000000000001</v>
+      </c>
+      <c r="G14" s="20">
+        <v>2.9990000000000001</v>
+      </c>
+      <c r="H14" s="20">
+        <v>2.9990000000000001</v>
+      </c>
+      <c r="I14" s="20">
+        <v>2.9990000000000001</v>
+      </c>
+      <c r="J14" s="20">
+        <v>3</v>
+      </c>
+      <c r="K14" s="20">
+        <v>3</v>
+      </c>
+      <c r="L14" s="20">
+        <v>2.992</v>
+      </c>
+      <c r="M14" s="20">
+        <v>0.1</v>
+      </c>
+      <c r="N14" s="20">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/src/prommis/solvent_extraction/SX_optimization_results.xlsx
+++ b/src/prommis/solvent_extraction/SX_optimization_results.xlsx
@@ -8,21 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ad00105\Desktop\Model_software\prommis\src\prommis\solvent_extraction\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B74C2C2F-F158-4BB1-B7EB-4BD1C413464F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4A07779-58D7-4EB2-A936-792EAB98B2B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-25320" yWindow="1785" windowWidth="25440" windowHeight="15270" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet4" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="0" iterate="1" iterateCount="10000"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="18">
   <si>
     <t>lb</t>
   </si>
@@ -34,9 +35,6 @@
   </si>
   <si>
     <t>Loading extractant dosage (%v/v)</t>
-  </si>
-  <si>
-    <t>Load inlet flowrate (L/hr)</t>
   </si>
   <si>
     <t>Scrubbing acid (M)</t>
@@ -69,10 +67,13 @@
     <t>load interstage 2 flowrate (L/hr)</t>
   </si>
   <si>
-    <t>load interstage 3 flowrate (L/hr)</t>
+    <t>strip interstage 1 flowrate (L/hr)</t>
   </si>
   <si>
-    <t>strip interstage 1 flowrate (L/hr)</t>
+    <t>Load inlet flowrate (L/hr)</t>
+  </si>
+  <si>
+    <t>load interstage 3 flowrate (L/hr)</t>
   </si>
   <si>
     <t>strip interstage 2 flowrate (L/hr)</t>
@@ -82,7 +83,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -121,8 +122,14 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -159,8 +166,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -213,11 +226,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -265,17 +293,25 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <mruColors>
-      <color rgb="FFFFFF81"/>
-    </mruColors>
-  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -285,6 +321,1924 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet3!$D$18:$D$28</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>5.8999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.05</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.04</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.03</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.02</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.01</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>5.0000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2E-3</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1E-3</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>5.0000000000000001E-4</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2.5000000000000001E-4</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet3!$E$18:$E$28</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>31.585999999999999</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>31.489000000000001</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>31.343</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>31.14</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>30.827000000000002</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>30.209</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>29.48</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>28.632000000000001</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>27.324999999999999</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>26.201000000000001</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>24.972999999999999</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-655C-460F-9DCB-0EF80BD7704E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="279719936"/>
+        <c:axId val="279722336"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="279719936"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="6.0000000000000012E-2"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="279722336"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="279722336"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:min val="20"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="279719936"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet4!$B$19:$B$31</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="13"/>
+                <c:pt idx="0">
+                  <c:v>0.417823</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.29998900000000001</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.199993</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>9.9996999999999989E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4.9998999999999988E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6.9997999999999991E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2.9999000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.01</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>7.0000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>5.0000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>3.0000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1E-3</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1E-3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet4!$C$19:$C$31</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="13"/>
+                <c:pt idx="0">
+                  <c:v>75.088999999999999</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>75.010999999999996</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>74.909000000000006</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>74.713999999999999</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>74.494</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>74.603999999999999</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>74.313999999999993</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>73.87</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>73.707999999999998</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>73.545000000000002</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>73.28</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>72.626999999999995</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>72.626999999999995</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-7DBE-4886-9BAD-4EB013F32BE4}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="280514672"/>
+        <c:axId val="281484352"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="280514672"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="281484352"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="281484352"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="280514672"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>119062</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>495300</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>4762</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1C9C9B95-D14B-504E-63B0-8E3128310540}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>4762</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>80962</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Chart 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{84B58787-92AC-5DBA-DAF7-CBFF5D89C779}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -674,7 +2628,7 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="B4" s="7">
         <v>60.01</v>
@@ -705,7 +2659,7 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B5" s="7">
         <v>0.1</v>
@@ -736,7 +2690,7 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6" s="7">
         <v>6</v>
@@ -767,7 +2721,7 @@
     </row>
     <row r="7" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B7" s="5">
         <v>9.5670000000000002</v>
@@ -796,7 +2750,7 @@
     </row>
     <row r="8" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B8" s="5">
         <v>3.0920000000000001</v>
@@ -825,7 +2779,7 @@
     </row>
     <row r="9" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B9" s="8">
         <v>3000</v>
@@ -860,7 +2814,7 @@
     </row>
     <row r="10" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B10" s="8">
         <v>3</v>
@@ -895,7 +2849,7 @@
     </row>
     <row r="11" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B11" s="8">
         <v>20.010000000000002</v>
@@ -930,7 +2884,7 @@
     </row>
     <row r="12" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B12" s="8">
         <v>89.296999999999997</v>
@@ -965,7 +2919,7 @@
     </row>
     <row r="13" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B13" s="8">
         <v>3</v>
@@ -1000,7 +2954,7 @@
     </row>
     <row r="14" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B14" s="8">
         <v>3</v>
@@ -1035,7 +2989,7 @@
     </row>
     <row r="15" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B15" s="8">
         <v>3</v>
@@ -1070,7 +3024,7 @@
     </row>
     <row r="16" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="9" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B16" s="8">
         <v>2.6110000000000002</v>
@@ -1235,7 +3189,7 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="B4" s="7">
         <v>60.01</v>
@@ -1264,7 +3218,7 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B5" s="8">
         <v>0.1</v>
@@ -1290,7 +3244,7 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6" s="8">
         <v>6</v>
@@ -1316,7 +3270,7 @@
     </row>
     <row r="7" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B7" s="8">
         <v>11.682</v>
@@ -1342,7 +3296,7 @@
     </row>
     <row r="8" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B8" s="8">
         <v>14.815</v>
@@ -1368,7 +3322,7 @@
     </row>
     <row r="9" spans="1:11" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B9" s="8">
         <v>3000</v>
@@ -1400,7 +3354,7 @@
     </row>
     <row r="10" spans="1:11" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B10" s="8">
         <v>3</v>
@@ -1432,7 +3386,7 @@
     </row>
     <row r="11" spans="1:11" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B11" s="8">
         <v>20.010000000000002</v>
@@ -1464,7 +3418,7 @@
     </row>
     <row r="12" spans="1:11" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B12" s="8">
         <v>89.715000000000003</v>
@@ -1496,7 +3450,7 @@
     </row>
     <row r="13" spans="1:11" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B13" s="8">
         <v>3</v>
@@ -1528,7 +3482,7 @@
     </row>
     <row r="14" spans="1:11" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B14" s="8">
         <v>3</v>
@@ -1560,7 +3514,7 @@
     </row>
     <row r="15" spans="1:11" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B15" s="8">
         <v>3</v>
@@ -1592,7 +3546,7 @@
     </row>
     <row r="16" spans="1:11" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B16" s="8">
         <v>2.7410000000000001</v>
@@ -1661,11 +3615,11 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:N28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.140625" style="8"/>
+    <col min="2" max="2" width="9.140625" style="8" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
@@ -1787,7 +3741,7 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="16" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B4" s="8">
         <v>0.1</v>
@@ -1825,7 +3779,7 @@
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="16" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B5" s="8">
         <v>6</v>
@@ -1863,7 +3817,7 @@
     </row>
     <row r="6" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="17" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B6" s="8">
         <v>31.585999999999999</v>
@@ -1901,7 +3855,7 @@
     </row>
     <row r="7" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="17" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B7" s="8">
         <v>5.8999999999999997E-2</v>
@@ -1939,7 +3893,7 @@
     </row>
     <row r="8" spans="1:14" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="19" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B8" s="8">
         <v>4999.1229999999996</v>
@@ -1983,7 +3937,7 @@
     </row>
     <row r="9" spans="1:14" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="19" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B9" s="8">
         <v>0.56300000000000006</v>
@@ -2027,7 +3981,7 @@
     </row>
     <row r="10" spans="1:14" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B10" s="8">
         <v>20.010000000000002</v>
@@ -2071,7 +4025,7 @@
     </row>
     <row r="11" spans="1:14" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B11" s="8">
         <v>79.92</v>
@@ -2115,7 +4069,7 @@
     </row>
     <row r="12" spans="1:14" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B12" s="8">
         <v>3</v>
@@ -2159,7 +4113,7 @@
     </row>
     <row r="13" spans="1:14" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="19" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B13" s="8">
         <v>3</v>
@@ -2203,7 +4157,7 @@
     </row>
     <row r="14" spans="1:14" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="19" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B14" s="8">
         <v>2.827</v>
@@ -2245,7 +4199,838 @@
         <v>3</v>
       </c>
     </row>
+    <row r="18" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D18" s="8">
+        <v>5.8999999999999997E-2</v>
+      </c>
+      <c r="E18" s="8">
+        <v>31.585999999999999</v>
+      </c>
+    </row>
+    <row r="19" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D19" s="5">
+        <v>0.05</v>
+      </c>
+      <c r="E19" s="5">
+        <v>31.489000000000001</v>
+      </c>
+    </row>
+    <row r="20" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D20" s="5">
+        <v>0.04</v>
+      </c>
+      <c r="E20" s="5">
+        <v>31.343</v>
+      </c>
+    </row>
+    <row r="21" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D21" s="5">
+        <v>0.03</v>
+      </c>
+      <c r="E21" s="5">
+        <v>31.14</v>
+      </c>
+    </row>
+    <row r="22" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D22" s="5">
+        <v>0.02</v>
+      </c>
+      <c r="E22" s="5">
+        <v>30.827000000000002</v>
+      </c>
+    </row>
+    <row r="23" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D23" s="5">
+        <v>0.01</v>
+      </c>
+      <c r="E23" s="5">
+        <v>30.209</v>
+      </c>
+    </row>
+    <row r="24" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D24" s="5">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="E24" s="5">
+        <v>29.48</v>
+      </c>
+    </row>
+    <row r="25" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D25" s="5">
+        <v>2E-3</v>
+      </c>
+      <c r="E25" s="5">
+        <v>28.632000000000001</v>
+      </c>
+    </row>
+    <row r="26" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D26" s="5">
+        <v>1E-3</v>
+      </c>
+      <c r="E26" s="5">
+        <v>27.324999999999999</v>
+      </c>
+    </row>
+    <row r="27" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D27" s="5">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="E27" s="5">
+        <v>26.201000000000001</v>
+      </c>
+    </row>
+    <row r="28" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D28" s="5">
+        <v>2.5000000000000001E-4</v>
+      </c>
+      <c r="E28" s="5">
+        <v>24.972999999999999</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:N31"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="32.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B1" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1" s="21">
+        <v>2</v>
+      </c>
+      <c r="D1" s="21">
+        <v>3</v>
+      </c>
+      <c r="E1" s="21">
+        <v>4</v>
+      </c>
+      <c r="F1" s="21">
+        <v>5</v>
+      </c>
+      <c r="G1" s="21">
+        <v>6</v>
+      </c>
+      <c r="H1" s="21">
+        <v>7</v>
+      </c>
+      <c r="I1" s="21">
+        <v>8</v>
+      </c>
+      <c r="J1" s="21">
+        <v>9</v>
+      </c>
+      <c r="K1" s="21">
+        <v>10</v>
+      </c>
+      <c r="L1" s="21">
+        <v>11</v>
+      </c>
+      <c r="M1" s="21">
+        <v>12</v>
+      </c>
+      <c r="N1" s="21">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A2" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="8">
+        <v>1.3</v>
+      </c>
+      <c r="C2">
+        <v>1.3</v>
+      </c>
+      <c r="D2">
+        <v>1.3</v>
+      </c>
+      <c r="E2">
+        <v>1.3</v>
+      </c>
+      <c r="F2">
+        <v>1.3</v>
+      </c>
+      <c r="G2">
+        <v>1.3</v>
+      </c>
+      <c r="H2">
+        <v>1.3</v>
+      </c>
+      <c r="I2">
+        <v>1.3</v>
+      </c>
+      <c r="J2">
+        <v>1.3</v>
+      </c>
+      <c r="K2">
+        <v>1.3</v>
+      </c>
+      <c r="L2">
+        <v>1.3</v>
+      </c>
+      <c r="M2">
+        <v>1.3</v>
+      </c>
+      <c r="N2">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A3" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="8">
+        <v>24.999989085599999</v>
+      </c>
+      <c r="C3">
+        <v>24.999985830899998</v>
+      </c>
+      <c r="D3">
+        <v>24.9999855286</v>
+      </c>
+      <c r="E3">
+        <v>24.999984966300001</v>
+      </c>
+      <c r="F3">
+        <v>24.999984340299999</v>
+      </c>
+      <c r="G3">
+        <v>24.999984652599998</v>
+      </c>
+      <c r="H3">
+        <v>24.999983833200002</v>
+      </c>
+      <c r="I3">
+        <v>24.999982587600002</v>
+      </c>
+      <c r="J3">
+        <v>24.999982129100001</v>
+      </c>
+      <c r="K3">
+        <v>24.9999816674</v>
+      </c>
+      <c r="L3">
+        <v>24.999980903899999</v>
+      </c>
+      <c r="M3">
+        <v>24.999978926800001</v>
+      </c>
+      <c r="N3">
+        <v>24.99997892679102</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A4" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="8">
+        <v>0.1</v>
+      </c>
+      <c r="C4">
+        <v>0.1</v>
+      </c>
+      <c r="D4">
+        <v>0.1</v>
+      </c>
+      <c r="E4">
+        <v>0.1</v>
+      </c>
+      <c r="F4">
+        <v>0.1</v>
+      </c>
+      <c r="G4">
+        <v>0.1</v>
+      </c>
+      <c r="H4">
+        <v>0.1</v>
+      </c>
+      <c r="I4">
+        <v>0.1</v>
+      </c>
+      <c r="J4">
+        <v>0.1</v>
+      </c>
+      <c r="K4">
+        <v>0.1</v>
+      </c>
+      <c r="L4">
+        <v>0.1</v>
+      </c>
+      <c r="M4">
+        <v>0.1</v>
+      </c>
+      <c r="N4">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A5" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="8">
+        <v>6</v>
+      </c>
+      <c r="C5">
+        <v>6</v>
+      </c>
+      <c r="D5">
+        <v>6</v>
+      </c>
+      <c r="E5">
+        <v>6</v>
+      </c>
+      <c r="F5">
+        <v>6</v>
+      </c>
+      <c r="G5">
+        <v>6</v>
+      </c>
+      <c r="H5">
+        <v>6</v>
+      </c>
+      <c r="I5">
+        <v>6</v>
+      </c>
+      <c r="J5">
+        <v>6</v>
+      </c>
+      <c r="K5">
+        <v>6</v>
+      </c>
+      <c r="L5">
+        <v>6</v>
+      </c>
+      <c r="M5">
+        <v>6</v>
+      </c>
+      <c r="N5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="8">
+        <v>75.088999999999999</v>
+      </c>
+      <c r="C6" s="5">
+        <v>75.010999999999996</v>
+      </c>
+      <c r="D6" s="5">
+        <v>74.909000000000006</v>
+      </c>
+      <c r="E6" s="5">
+        <v>74.713999999999999</v>
+      </c>
+      <c r="F6" s="5">
+        <v>74.494</v>
+      </c>
+      <c r="G6" s="5">
+        <v>74.603999999999999</v>
+      </c>
+      <c r="H6" s="5">
+        <v>74.313999999999993</v>
+      </c>
+      <c r="I6" s="5">
+        <v>73.87</v>
+      </c>
+      <c r="J6" s="5">
+        <v>73.707999999999998</v>
+      </c>
+      <c r="K6" s="5">
+        <v>73.545000000000002</v>
+      </c>
+      <c r="L6" s="5">
+        <v>73.28</v>
+      </c>
+      <c r="M6" s="5">
+        <v>72.626999999999995</v>
+      </c>
+      <c r="N6" s="5">
+        <v>72.626999999999995</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A7" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="8">
+        <v>0.417823</v>
+      </c>
+      <c r="C7" s="5">
+        <v>0.29998900000000001</v>
+      </c>
+      <c r="D7" s="5">
+        <v>0.199993</v>
+      </c>
+      <c r="E7" s="5">
+        <v>9.9996999999999989E-2</v>
+      </c>
+      <c r="F7" s="5">
+        <v>4.9998999999999988E-2</v>
+      </c>
+      <c r="G7" s="5">
+        <v>6.9997999999999991E-2</v>
+      </c>
+      <c r="H7" s="5">
+        <v>2.9999000000000001E-2</v>
+      </c>
+      <c r="I7" s="5">
+        <v>0.01</v>
+      </c>
+      <c r="J7" s="5">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="K7" s="5">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="L7" s="5">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="M7" s="5">
+        <v>1E-3</v>
+      </c>
+      <c r="N7" s="5">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A8" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="8">
+        <v>5999.8329999999996</v>
+      </c>
+      <c r="C8" s="23">
+        <v>5999.9989999999998</v>
+      </c>
+      <c r="D8" s="23">
+        <v>5999.9989999999998</v>
+      </c>
+      <c r="E8" s="23">
+        <v>5999.9989999999998</v>
+      </c>
+      <c r="F8" s="23">
+        <v>6000</v>
+      </c>
+      <c r="G8" s="23">
+        <v>6000</v>
+      </c>
+      <c r="H8" s="23">
+        <v>6000</v>
+      </c>
+      <c r="I8" s="23">
+        <v>6000</v>
+      </c>
+      <c r="J8" s="23">
+        <v>6000</v>
+      </c>
+      <c r="K8" s="23">
+        <v>6000</v>
+      </c>
+      <c r="L8" s="23">
+        <v>6000</v>
+      </c>
+      <c r="M8" s="23">
+        <v>6000</v>
+      </c>
+      <c r="N8" s="23">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A9" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="8">
+        <v>0.57200000000000006</v>
+      </c>
+      <c r="C9" s="23">
+        <v>0.57000000000000006</v>
+      </c>
+      <c r="D9" s="23">
+        <v>0.56700000000000006</v>
+      </c>
+      <c r="E9" s="23">
+        <v>0.56200000000000006</v>
+      </c>
+      <c r="F9" s="23">
+        <v>0.55600000000000005</v>
+      </c>
+      <c r="G9" s="23">
+        <v>0.55900000000000005</v>
+      </c>
+      <c r="H9" s="23">
+        <v>0.55100000000000005</v>
+      </c>
+      <c r="I9" s="23">
+        <v>0.53900000000000003</v>
+      </c>
+      <c r="J9" s="23">
+        <v>0.53500000000000003</v>
+      </c>
+      <c r="K9" s="23">
+        <v>0.53100000000000003</v>
+      </c>
+      <c r="L9" s="23">
+        <v>0.52400000000000002</v>
+      </c>
+      <c r="M9" s="23">
+        <v>0.50700000000000001</v>
+      </c>
+      <c r="N9" s="23">
+        <v>0.50700000000000001</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A10" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="8">
+        <v>5.01</v>
+      </c>
+      <c r="C10" s="23">
+        <v>5.01</v>
+      </c>
+      <c r="D10" s="23">
+        <v>5.01</v>
+      </c>
+      <c r="E10" s="23">
+        <v>5.01</v>
+      </c>
+      <c r="F10" s="23">
+        <v>5.01</v>
+      </c>
+      <c r="G10" s="23">
+        <v>5.01</v>
+      </c>
+      <c r="H10" s="23">
+        <v>5.01</v>
+      </c>
+      <c r="I10" s="23">
+        <v>5.01</v>
+      </c>
+      <c r="J10" s="23">
+        <v>5.01</v>
+      </c>
+      <c r="K10" s="23">
+        <v>5.01</v>
+      </c>
+      <c r="L10" s="23">
+        <v>5.01</v>
+      </c>
+      <c r="M10" s="23">
+        <v>5.01</v>
+      </c>
+      <c r="N10" s="23">
+        <v>5.01</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A11" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" s="8">
+        <v>79.992000000000004</v>
+      </c>
+      <c r="C11" s="23">
+        <v>80.007000000000005</v>
+      </c>
+      <c r="D11" s="23">
+        <v>80.007000000000005</v>
+      </c>
+      <c r="E11" s="23">
+        <v>80.007999999999996</v>
+      </c>
+      <c r="F11" s="23">
+        <v>80.007999999999996</v>
+      </c>
+      <c r="G11" s="23">
+        <v>80.007999999999996</v>
+      </c>
+      <c r="H11" s="23">
+        <v>80.007999999999996</v>
+      </c>
+      <c r="I11" s="23">
+        <v>80.007999999999996</v>
+      </c>
+      <c r="J11" s="23">
+        <v>80.009</v>
+      </c>
+      <c r="K11" s="23">
+        <v>80.009</v>
+      </c>
+      <c r="L11" s="23">
+        <v>80.009</v>
+      </c>
+      <c r="M11" s="23">
+        <v>80.009</v>
+      </c>
+      <c r="N11" s="23">
+        <v>80.009</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A12" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" s="8">
+        <v>3</v>
+      </c>
+      <c r="C12" s="23">
+        <v>3</v>
+      </c>
+      <c r="D12" s="23">
+        <v>3</v>
+      </c>
+      <c r="E12" s="23">
+        <v>3</v>
+      </c>
+      <c r="F12" s="23">
+        <v>3</v>
+      </c>
+      <c r="G12" s="23">
+        <v>3</v>
+      </c>
+      <c r="H12" s="23">
+        <v>3</v>
+      </c>
+      <c r="I12" s="23">
+        <v>3</v>
+      </c>
+      <c r="J12" s="23">
+        <v>3</v>
+      </c>
+      <c r="K12" s="23">
+        <v>3</v>
+      </c>
+      <c r="L12" s="23">
+        <v>3</v>
+      </c>
+      <c r="M12" s="23">
+        <v>3</v>
+      </c>
+      <c r="N12" s="23">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A13" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" s="8">
+        <v>3</v>
+      </c>
+      <c r="C13" s="23">
+        <v>3</v>
+      </c>
+      <c r="D13" s="23">
+        <v>3</v>
+      </c>
+      <c r="E13" s="23">
+        <v>3</v>
+      </c>
+      <c r="F13" s="23">
+        <v>3</v>
+      </c>
+      <c r="G13" s="23">
+        <v>3</v>
+      </c>
+      <c r="H13" s="23">
+        <v>3</v>
+      </c>
+      <c r="I13" s="23">
+        <v>3</v>
+      </c>
+      <c r="J13" s="23">
+        <v>3</v>
+      </c>
+      <c r="K13" s="23">
+        <v>3</v>
+      </c>
+      <c r="L13" s="23">
+        <v>3</v>
+      </c>
+      <c r="M13" s="23">
+        <v>3</v>
+      </c>
+      <c r="N13" s="23">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A14" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" s="8">
+        <v>3.964</v>
+      </c>
+      <c r="C14" s="23">
+        <v>3.9969999999999999</v>
+      </c>
+      <c r="D14" s="23">
+        <v>3.9969999999999999</v>
+      </c>
+      <c r="E14" s="23">
+        <v>3.9980000000000002</v>
+      </c>
+      <c r="F14" s="23">
+        <v>3.9980000000000002</v>
+      </c>
+      <c r="G14" s="23">
+        <v>3.9980000000000002</v>
+      </c>
+      <c r="H14" s="23">
+        <v>3.9980000000000002</v>
+      </c>
+      <c r="I14" s="23">
+        <v>3.9980000000000002</v>
+      </c>
+      <c r="J14" s="23">
+        <v>3.9980000000000002</v>
+      </c>
+      <c r="K14" s="23">
+        <v>3.9990000000000001</v>
+      </c>
+      <c r="L14" s="23">
+        <v>3.9990000000000001</v>
+      </c>
+      <c r="M14" s="23">
+        <v>3.9990000000000001</v>
+      </c>
+      <c r="N14" s="23">
+        <v>3.9990000000000001</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B19" s="8">
+        <v>0.417823</v>
+      </c>
+      <c r="C19" s="8">
+        <v>75.088999999999999</v>
+      </c>
+      <c r="E19" s="8"/>
+    </row>
+    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B20" s="5">
+        <v>0.29998900000000001</v>
+      </c>
+      <c r="C20" s="5">
+        <v>75.010999999999996</v>
+      </c>
+      <c r="E20" s="5"/>
+    </row>
+    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B21" s="5">
+        <v>0.199993</v>
+      </c>
+      <c r="C21" s="5">
+        <v>74.909000000000006</v>
+      </c>
+      <c r="E21" s="5"/>
+    </row>
+    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B22" s="5">
+        <v>9.9996999999999989E-2</v>
+      </c>
+      <c r="C22" s="5">
+        <v>74.713999999999999</v>
+      </c>
+      <c r="E22" s="5"/>
+    </row>
+    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B23" s="5">
+        <v>4.9998999999999988E-2</v>
+      </c>
+      <c r="C23" s="5">
+        <v>74.494</v>
+      </c>
+      <c r="E23" s="5"/>
+    </row>
+    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B24" s="5">
+        <v>6.9997999999999991E-2</v>
+      </c>
+      <c r="C24" s="5">
+        <v>74.603999999999999</v>
+      </c>
+      <c r="E24" s="5"/>
+    </row>
+    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B25" s="5">
+        <v>2.9999000000000001E-2</v>
+      </c>
+      <c r="C25" s="5">
+        <v>74.313999999999993</v>
+      </c>
+      <c r="E25" s="5"/>
+    </row>
+    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B26" s="5">
+        <v>0.01</v>
+      </c>
+      <c r="C26" s="5">
+        <v>73.87</v>
+      </c>
+      <c r="E26" s="5"/>
+    </row>
+    <row r="27" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B27" s="5">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="C27" s="5">
+        <v>73.707999999999998</v>
+      </c>
+      <c r="E27" s="5"/>
+    </row>
+    <row r="28" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B28" s="5">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="C28" s="5">
+        <v>73.545000000000002</v>
+      </c>
+      <c r="E28" s="5"/>
+    </row>
+    <row r="29" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B29" s="5">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="C29" s="5">
+        <v>73.28</v>
+      </c>
+      <c r="E29" s="5"/>
+    </row>
+    <row r="30" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B30" s="5">
+        <v>1E-3</v>
+      </c>
+      <c r="C30" s="5">
+        <v>72.626999999999995</v>
+      </c>
+    </row>
+    <row r="31" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B31" s="5">
+        <v>1E-3</v>
+      </c>
+      <c r="C31" s="5">
+        <v>72.626999999999995</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>